--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -842,22 +834,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -890,12 +882,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -953,7 +945,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -963,7 +955,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1228 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1187,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1220,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1244,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1865,7 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1843,7 +1875,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1881,12 +1913,12 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1900,7 +1932,7 @@
       <c r="T13" s="2" t="inlineStr"/>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2087,7 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2065,7 +2097,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2103,12 +2135,12 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2122,7 +2154,7 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -2166,22 +2198,22 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2214,12 +2246,12 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2233,7 +2265,7 @@
       <c r="T16" s="2" t="inlineStr"/>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2258,7 +2290,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2269,7 +2301,800 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       <c r="T19" s="2" t="inlineStr"/>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3098,6 +3098,339 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1441,32 +1441,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1474,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,17 +1502,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1518,13 +1522,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1560,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1585,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1621,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1679,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1696,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1740,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1798,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1807,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,17 +1859,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1851,13 +1879,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1996,32 +2028,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2029,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,33 +2089,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2179,7 +2219,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2251,7 +2291,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2290,7 +2330,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2329,32 +2369,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2362,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2386,17 +2430,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2406,17 +2450,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2627,7 +2671,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2642,7 +2686,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2747,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2818,7 +2862,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2857,7 +2901,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2929,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3088,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3083,7 +3127,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3102,7 +3146,7 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3150,12 +3194,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3223,7 +3267,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3266,7 +3310,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3280,7 +3324,7 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3310,13 +3354,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3324,22 +3372,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3372,12 +3420,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3391,7 +3439,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3426,6 +3474,1025 @@
       </c>
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>—/17</t>
         </is>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,13 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1302,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1402,18 +1406,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1532,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,7 +1763,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1770,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1889,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,17 +2117,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2291,7 +2299,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,24 +2387,24 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2406,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2455,12 +2463,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,7 +2640,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2686,7 +2694,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2755,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2786,7 +2794,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2801,7 +2809,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -2809,22 +2817,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2857,12 +2865,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2876,7 +2884,7 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2901,18 +2909,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -2920,60 +2932,64 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2987,7 +3003,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2997,22 +3013,22 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3022,12 +3038,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3051,7 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3045,7 +3061,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3055,40 +3071,44 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3102,7 +3122,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3112,33 +3132,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3170,22 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3194,12 +3218,12 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3213,7 +3237,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3243,13 +3267,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -3257,52 +3285,56 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3310,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3324,7 +3356,7 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3334,22 +3366,22 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3359,12 +3391,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3404,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3420,12 +3452,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3483,7 +3515,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3493,7 +3525,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3531,12 +3563,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3550,7 +3582,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3580,13 +3612,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -3594,22 +3630,22 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3647,7 +3683,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3686,7 +3722,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3696,12 +3732,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -3709,22 +3745,22 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3757,12 +3793,12 @@
       <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3776,7 +3812,7 @@
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3801,7 +3837,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3811,12 +3847,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3824,60 +3860,64 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3891,7 +3931,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3901,17 +3941,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3921,17 +3961,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3939,22 +3979,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3987,12 +4027,12 @@
       <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4006,7 +4046,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -4036,17 +4076,13 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -4054,22 +4090,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4102,12 +4138,12 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4121,7 +4157,7 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4146,18 +4182,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4165,22 +4205,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4213,12 +4253,12 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:39</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4232,7 +4272,7 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4257,22 +4297,18 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -4280,22 +4316,22 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4328,12 +4364,12 @@
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>06:39</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4347,7 +4383,7 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4372,18 +4408,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -4391,22 +4431,22 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4439,12 +4479,12 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4488,13 +4528,477 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>109.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1649,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,18 +2227,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,13 +2347,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2476,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2679,22 +2687,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2794,17 +2802,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2870,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2924,7 +2932,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3028,7 +3036,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3043,7 +3051,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3170,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3262,7 +3270,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3277,7 +3285,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3396,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3535,32 +3543,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3568,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3592,17 +3604,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3612,17 +3624,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -3650,32 +3662,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3683,7 +3699,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3707,17 +3723,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3727,17 +3743,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -3765,32 +3781,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3798,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3822,17 +3842,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3842,12 +3862,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3890,24 +3910,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3917,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3956,22 +3976,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -3999,32 +4019,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4032,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4056,33 +4080,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -4110,32 +4138,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4143,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4167,37 +4199,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4225,32 +4257,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:39</t>
@@ -4258,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4282,17 +4318,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4302,13 +4338,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4408,7 +4448,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4423,7 +4463,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4484,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4538,7 +4578,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -4566,32 +4606,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4599,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4623,32 +4667,32 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4714,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4768,7 +4812,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4873,17 +4917,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4891,22 +4935,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4939,12 +4983,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4958,47 +5002,852 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>12/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>109.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>11/17</t>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>12/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,22 +2227,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,17 +2692,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3270,22 +3270,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3857,22 +3857,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,22 +3976,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4095,22 +4095,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4616,24 +4616,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -4955,32 +4955,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4988,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5012,37 +5016,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -5070,32 +5074,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5103,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5127,37 +5135,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -5185,32 +5193,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5218,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5242,37 +5254,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5312,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5333,7 +5349,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5357,37 +5373,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -5415,32 +5431,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5448,7 +5468,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5472,17 +5492,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5492,17 +5512,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5602,7 +5622,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5612,12 +5632,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5698,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5740,7 +5760,7 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5793,7 +5813,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5832,20 +5852,825 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
+      <c r="AA48" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>12/17</t>
         </is>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6676,6 +6676,121 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2122,12 +2122,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,22 +2461,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,22 +3036,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4448,22 +4448,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5203,24 +5203,24 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5322,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5530,60 +5530,64 @@
       <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5597,7 +5601,7 @@
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5607,17 +5611,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5632,12 +5636,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -5645,60 +5649,64 @@
       <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5712,7 +5720,7 @@
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5722,37 +5730,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5768,7 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5813,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5862,12 +5870,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -5875,22 +5883,22 @@
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5928,7 +5936,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5942,7 +5950,7 @@
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5972,17 +5980,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -5990,60 +5998,64 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>29分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6057,7 +6069,7 @@
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -6067,17 +6079,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6087,17 +6099,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>1/17</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6117,7 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -6153,12 +6165,12 @@
       <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6197,7 +6209,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6207,12 +6219,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -6220,22 +6232,22 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6268,12 +6280,12 @@
       <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6287,7 +6299,7 @@
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -6312,22 +6324,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -6335,22 +6347,22 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6383,12 +6395,12 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6402,7 +6414,7 @@
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -6437,12 +6449,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -6450,22 +6462,22 @@
       <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6498,12 +6510,12 @@
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6517,7 +6529,7 @@
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -6547,17 +6559,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6565,22 +6577,22 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6613,12 +6625,12 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6632,7 +6644,7 @@
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6657,22 +6669,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -6680,22 +6692,22 @@
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6733,7 +6745,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6747,7 +6759,7 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6772,22 +6784,367 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB54" s="2" t="inlineStr">
-        <is>
-          <t>88.3</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
         <is>
           <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1763,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3857,22 +3857,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5150,22 +5150,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5393,17 +5393,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5679,19 +5679,19 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5903,32 +5903,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5936,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5960,17 +5964,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5980,12 +5984,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6055,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6209,7 +6213,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6252,32 +6256,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6285,7 +6293,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6309,37 +6317,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6408,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6439,7 +6447,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6454,7 +6462,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6482,32 +6490,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6515,7 +6527,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6539,17 +6551,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6559,17 +6571,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -6630,7 +6642,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6757,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6860,7 +6872,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6914,7 +6926,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6987,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7024,12 +7036,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7102,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7134,17 +7146,584 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,17 +3981,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4214,17 +4214,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq22推进至seq35，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4532,10 +4532,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4563,7 +4575,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4643,7 +4655,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4682,22 +4694,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4770,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,12 +4852,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq24推进至seq28，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4873,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4881,10 +4893,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -4912,7 +4936,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4992,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5165,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5274,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5349,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5388,7 +5412,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5403,7 +5427,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5507,17 +5531,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5587,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5631,17 +5655,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5745,22 +5769,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5845,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6103,12 +6127,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6174,7 +6198,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,7 +6317,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6347,7 +6371,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -6375,32 +6399,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6408,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6432,17 +6460,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6452,17 +6480,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6566,7 +6594,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6581,7 +6609,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6609,32 +6637,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6642,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6666,32 +6698,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6724,32 +6756,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6757,7 +6793,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6781,17 +6817,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6801,12 +6837,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6839,32 +6875,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6872,7 +6912,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6896,17 +6936,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6916,17 +6956,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -6954,32 +6994,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6987,7 +7031,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7011,37 +7055,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,7 +7376,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7386,7 +7430,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -7394,22 +7438,22 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7442,12 +7486,12 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7461,7 +7505,7 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7486,7 +7530,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7505,7 +7549,7 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -7553,12 +7597,12 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7597,18 +7641,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -7616,22 +7664,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7664,12 +7712,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7683,47 +7731,959 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>15:10</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA65" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
         <is>
           <t>8/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>12/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,18 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1306,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2242,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2537,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2648,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2702,7 +2706,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2817,7 +2821,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2932,7 +2936,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3040,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3051,7 +3055,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3270,22 +3274,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3389,22 +3393,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,18 +3508,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3634,7 +3642,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3753,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3857,22 +3865,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,7 +3984,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3991,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4110,7 +4118,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4229,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4409,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4448,7 +4456,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4463,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4590,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4709,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4809,22 +4817,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4865,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq24推进至seq28，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq24推进至seq38，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4885,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4951,7 +4959,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5055,22 +5063,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,22 +5182,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,7 +5301,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5308,7 +5316,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5427,7 +5435,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5554,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5650,7 +5658,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5665,7 +5673,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5792,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5884,22 +5892,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6003,22 +6011,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6237,22 +6245,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6356,22 +6364,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6475,7 +6483,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6490,7 +6498,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6609,7 +6617,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6728,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6951,7 +6959,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6966,7 +6974,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7085,7 +7093,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -7113,32 +7121,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7146,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7170,37 +7182,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -7228,32 +7240,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7261,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7285,37 +7301,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -7343,32 +7359,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7376,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7400,37 +7420,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7530,7 +7550,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7602,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7641,7 +7661,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7656,7 +7676,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -7684,32 +7704,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7717,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7741,33 +7765,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7856,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7882,7 +7910,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7971,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8082,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8108,7 +8136,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8197,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8223,7 +8251,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8312,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8338,7 +8366,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8427,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8461,22 +8489,22 @@
       <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8509,12 +8537,12 @@
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8528,7 +8556,7 @@
       <c r="T69" s="2" t="inlineStr"/>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
@@ -8553,22 +8581,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -8576,22 +8604,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8624,12 +8652,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8668,22 +8696,823 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>6/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,17 +2231,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,22 +2346,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2691,22 +2691,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,22 +2806,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,17 +4103,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4222,22 +4222,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4341,22 +4341,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,22 +4583,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,22 +4702,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5420,17 +5420,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5539,22 +5539,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5777,22 +5777,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6602,17 +6602,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,22 +6721,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -7396,7 +7396,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8049,32 +8049,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8082,7 +8086,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8106,32 +8110,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8164,32 +8168,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8197,7 +8205,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8221,37 +8229,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -8279,32 +8287,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8312,7 +8324,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8336,37 +8348,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8394,32 +8406,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:39</t>
@@ -8427,7 +8443,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8451,37 +8467,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8558,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8581,7 +8597,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8624,32 +8640,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8657,7 +8677,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8681,37 +8701,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8792,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8887,7 +8907,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8941,7 +8961,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9022,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9041,7 +9061,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9056,7 +9076,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -9117,7 +9137,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9232,7 +9252,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9343,7 +9363,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9458,7 +9478,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9512,7 +9532,1038 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>15/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>4/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>13/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,18 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2246,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2541,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2580,7 +2584,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2652,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2706,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2816,12 +2820,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2921,7 +2925,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2936,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3040,7 +3044,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3055,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3279,12 +3283,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3354,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,17 +3402,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3508,22 +3512,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3642,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3826,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3865,22 +3869,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,17 +3993,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4237,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4456,7 +4460,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4471,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,7 +4587,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4598,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4712,12 +4716,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4822,17 +4826,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5024,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,12 +5072,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5143,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,22 +5186,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5310,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5435,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5558,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,7 +5662,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5673,7 +5677,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5787,12 +5791,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,12 +5901,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5972,7 +5976,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,17 +6020,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6130,7 +6134,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6206,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,12 +6254,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6325,7 +6329,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6364,22 +6368,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6448,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,17 +6492,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6567,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6617,7 +6621,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6736,7 +6740,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6805,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,7 +6844,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6920,7 +6924,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6959,7 +6963,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6974,7 +6978,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7088,12 +7092,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7162,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7202,17 +7206,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7281,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,12 +7325,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7396,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7435,22 +7439,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7550,18 +7554,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7666,17 +7674,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7780,22 +7788,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7864,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7910,7 +7918,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7979,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8010,7 +8018,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8086,7 +8094,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8140,7 +8148,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8213,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8244,7 +8252,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8259,7 +8267,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -8324,7 +8332,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8378,7 +8386,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8451,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8497,7 +8505,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8566,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,12 +8658,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -8677,7 +8685,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8726,12 +8734,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8800,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8831,7 +8839,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8846,7 +8854,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -8874,32 +8882,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8907,7 +8919,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8931,17 +8943,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -8951,17 +8963,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -8989,32 +9001,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9022,7 +9038,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9046,17 +9062,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9066,12 +9082,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9104,32 +9120,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9137,7 +9157,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9161,37 +9181,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -9219,32 +9239,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9252,7 +9276,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9276,33 +9300,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -9330,32 +9358,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9363,7 +9395,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9387,17 +9419,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9407,17 +9439,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -9445,32 +9477,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9478,7 +9514,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9502,37 +9538,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9629,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9647,7 +9683,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9744,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9747,7 +9783,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9819,7 +9855,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9873,7 +9909,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9970,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -9973,7 +10009,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -9988,7 +10024,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10085,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10103,7 +10139,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10200,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10218,7 +10254,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -10279,7 +10315,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10328,12 +10364,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10430,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10509,7 +10545,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10553,17 +10589,818 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB86" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr">
-        <is>
-          <t>11/17</t>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>3/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,13 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2771,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2886,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3005,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3239,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3473,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3592,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3631,7 +3635,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3646,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3830,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3949,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3998,7 +4002,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4068,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4187,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4306,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4421,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4536,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4667,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4897,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5028,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5147,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5266,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5315,7 +5319,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5385,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5504,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5623,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5742,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5857,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6095,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6210,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6329,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6448,7 +6452,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6497,7 +6501,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6567,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6686,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6805,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7043,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7281,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7679,7 +7683,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7749,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7864,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7903,7 +7907,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7918,7 +7922,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -7979,7 +7983,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8023,13 +8027,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8213,7 +8221,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8332,7 +8340,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8451,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8566,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8685,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8800,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9038,7 +9046,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9157,7 +9165,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9276,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9368,12 +9376,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -9395,7 +9403,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9444,7 +9452,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9514,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9629,7 +9637,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9668,7 +9676,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9683,7 +9691,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -9711,32 +9719,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9744,7 +9756,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9768,17 +9780,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9788,13 +9800,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9871,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9970,7 +9986,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10085,7 +10101,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10200,7 +10216,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10315,7 +10331,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10430,7 +10446,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10545,7 +10561,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10660,7 +10676,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10775,7 +10791,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10890,7 +10906,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11005,7 +11021,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11120,7 +11136,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11164,13 +11180,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB91" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11251,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11346,7 +11366,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11404,6 +11424,121 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2819,17 +2819,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,17 +4116,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,22 +4349,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,17 +5076,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5433,17 +5433,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5790,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5905,17 +5905,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,17 +6615,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,17 +6734,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,17 +7091,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,17 +7329,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,17 +8265,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8384,17 +8384,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8498,22 +8498,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8737,17 +8737,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/17</t>
+          <t>3/17</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9090,17 +9090,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -9604,32 +9604,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9637,7 +9641,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9661,17 +9665,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9681,12 +9685,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9729,24 +9733,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9756,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9805,7 +9809,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9838,32 +9842,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9871,7 +9879,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9895,17 +9903,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9915,17 +9923,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -9953,32 +9961,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9986,7 +9998,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10010,17 +10022,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10030,17 +10042,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -10068,32 +10080,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:39</t>
@@ -10101,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10125,37 +10141,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -10183,32 +10199,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10216,7 +10236,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10240,17 +10260,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10260,17 +10280,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>6/17</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10318,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10331,7 +10355,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10355,17 +10379,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10375,17 +10399,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10485,7 +10509,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10528,32 +10552,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10561,7 +10589,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10585,17 +10613,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10605,17 +10633,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10704,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10730,7 +10758,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/17</t>
+          <t>2/17</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10819,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10830,7 +10858,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10906,7 +10934,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11021,7 +11049,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11075,7 +11103,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>4/17</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11164,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11185,7 +11213,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11251,7 +11279,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11305,7 +11333,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11394,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11410,17 +11438,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -11481,7 +11509,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11525,17 +11553,362 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>17/17</t>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/17</t>
+          <t>7/17</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,22 +3516,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3635,17 +3635,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4596,17 +4596,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,17 +7563,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7792,22 +7792,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,17 +8027,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8265,17 +8265,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9328,17 +9328,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9561,22 +9561,22 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9680,17 +9680,17 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9804,17 +9804,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10042,17 +10042,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>6/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -10671,32 +10671,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10704,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10728,17 +10732,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10748,7 +10752,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10786,32 +10790,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10819,7 +10827,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10843,17 +10851,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10863,12 +10871,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10901,32 +10909,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -10934,7 +10946,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10958,17 +10970,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10978,17 +10990,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -11016,32 +11028,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11049,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11073,17 +11089,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11093,12 +11109,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11131,32 +11147,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11164,7 +11184,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11188,17 +11208,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11208,17 +11228,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -11246,32 +11266,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -11279,7 +11303,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11303,37 +11327,37 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>5/17</t>
         </is>
       </c>
     </row>
@@ -11361,32 +11385,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11394,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11418,17 +11446,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11438,17 +11466,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -11476,32 +11504,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11509,7 +11541,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11533,32 +11565,32 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11624,7 +11656,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11678,7 +11710,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11771,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11778,7 +11810,7 @@
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -11793,7 +11825,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>7/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11886,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11898,17 +11930,362 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>79.4</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>1/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>5/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>77.8</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>1/17</t>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>96.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>17/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:39</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>10/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-19-浦东78路.xlsx
+++ b/data/export/2026-10-19-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3759,17 +3759,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4957,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8618,17 +8618,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -9933,7 +9933,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/17</t>
+          <t>10/17</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10514,17 +10514,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10827,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11422,7 +11422,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/17</t>
+          <t>9/17</t>
         </is>
       </c>
     </row>
@@ -11504,36 +11504,32 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11541,7 +11537,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11565,17 +11561,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11585,12 +11581,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11623,32 +11619,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11656,7 +11656,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11680,17 +11680,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11700,17 +11700,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>8/17</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11825,7 +11825,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -11853,32 +11853,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11886,7 +11890,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11910,17 +11914,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11930,12 +11934,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12001,7 +12005,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12116,7 +12120,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12160,12 +12164,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12231,7 +12235,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12285,7 +12289,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
